--- a/reports/appendix_v1/VOLT-FORGE_Appendix.xlsx
+++ b/reports/appendix_v1/VOLT-FORGE_Appendix.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="489">
   <si>
     <t xml:space="preserve">VOLT-FORGE appendix</t>
   </si>
@@ -76,10 +76,28 @@
     <t xml:space="preserve">Frozen plan, run once, every result kept</t>
   </si>
   <si>
+    <t xml:space="preserve">Nearest cell, real share of current at the start, %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Published four-cell test. The model predicted 34.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Farthest cell, real share of current at the start, %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same test. The model predicted 18.7</t>
+  </si>
+  <si>
     <t xml:space="preserve">Measured cases inside both bands</t>
   </si>
   <si>
-    <t xml:space="preserve">Out of 12. The model was not tuned to close this gap</t>
+    <t xml:space="preserve">Out of 12 full-discharge checks. Voltage and temperature both missed. The model was not tuned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Highest real over model heating, first 10 minutes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eight measured discharges, the length of the Pi job</t>
   </si>
   <si>
     <t xml:space="preserve">Cost to build the full product, ₹ crore</t>
@@ -118,6 +136,18 @@
     <t xml:space="preserve">Assumed 5% of engineering colleges</t>
   </si>
   <si>
+    <t xml:space="preserve">First stage of the build, ₹ crore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dataset, results, quality and the lab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paying teams to repay it in 5 years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At an assumed ₹5 lakh a year, plus 130 labs, before running costs</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tabs</t>
   </si>
   <si>
@@ -130,13 +160,13 @@
     <t xml:space="preserve">Market</t>
   </si>
   <si>
-    <t xml:space="preserve">TAM, SAM, SOM and how long licences alone take to repay the build</t>
+    <t xml:space="preserve">TAM, SAM, SOM, the staged business case and what it takes to repay it</t>
   </si>
   <si>
     <t xml:space="preserve">Parts</t>
   </si>
   <si>
-    <t xml:space="preserve">Listings and cost at each cell count</t>
+    <t xml:space="preserve">Listings and cost at each cell count, with the matching board</t>
   </si>
   <si>
     <t xml:space="preserve">Design study</t>
@@ -148,13 +178,13 @@
     <t xml:space="preserve">Evidence</t>
   </si>
   <si>
-    <t xml:space="preserve">Software checks and the comparison with real measurements</t>
+    <t xml:space="preserve">Software checks, real measurements, and whether the error changes the decision</t>
   </si>
   <si>
     <t xml:space="preserve">Limits and sources</t>
   </si>
   <si>
-    <t xml:space="preserve">What is untested, and where each number came from</t>
+    <t xml:space="preserve">What is untested, bench safety, and where each number came from</t>
   </si>
   <si>
     <t xml:space="preserve">Colour key</t>
@@ -451,6 +481,9 @@
     <t xml:space="preserve">Our whole build as a share of one AspenTech year</t>
   </si>
   <si>
+    <t xml:space="preserve">Scale check only. AspenTech is not a battery tool, so this is not a like-for-like price.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Who could use it, India first</t>
   </si>
   <si>
@@ -529,7 +562,91 @@
     <t xml:space="preserve">Years of SOM revenue to repay the build</t>
   </si>
   <si>
-    <t xml:space="preserve">Lab licences alone will not repay a ₹35 crore build. The plan needs a paid tier for engineering teams. That price is not set yet.</t>
+    <t xml:space="preserve">Lab licences alone will not repay a ₹35 crore build, so the plan needs paying engineering teams and a staged build.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Business case (hypothesis, no customer has seen these prices)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free for students. Labs pay a yearly licence. Engineering teams pay a yearly team plan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MATLAB, US$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simulink, US$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simscape, US$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simscape Battery, US$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One commercial seat today, ₹ lakh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One seat of the nearest commercial stack. Perpetual, named user, North America Standard, September 2026, excluding tax.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Team plan, ₹ a year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One team, up to five seats. Placeholder set below one seat of the benchmark stack. Not tested with any customer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Years to repay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planning horizon for the first stage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost, ₹ crore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What is in it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Running total, ₹ crore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paying teams needed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Validated tool for labs and small teams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measured dataset and validation, Simulation, results, failure search and comparison, Quality, documentation and support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Pack scale for larger teams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electrical and thermal solvers to pack scale, Component library and versioned model graph, AI copilot, Reports, projects, collaboration and security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Full engineering suite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electrochemistry, CFD and FEA, 3D Design Studio and CAD exchange, Product, design and management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage one carries all lab equipment and lab running costs. Other shared costs are split by people cost, and contingency is added to each stage. Each stage starts only if the one before it is paying. Repayment leaves out running, support and sales costs after the build, and assumes customers from day one. The number of paying teams in India has not been sized.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stage one, needed a year, ₹ crore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paying teams needed with no lab income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Labs needed with no team income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Against 2,610 colleges, so labs alone are unlikely to carry it.</t>
   </si>
   <si>
     <t xml:space="preserve">What the backup would cost in parts</t>
@@ -607,22 +724,28 @@
     <t xml:space="preserve">Indicative rate per kg for a 12 mm busbar. Not a quote for thin fabricated links.</t>
   </si>
   <si>
+    <t xml:space="preserve">Geekworm X1205 2-cell UPS HAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geekworm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contradictory on the page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Batteries, shipping and import duty not included. The page showed both "Only 118 items in stock" and "Out of stock". Lists up to 95% efficiency and a 2.4 V over-discharge cutoff on v1.1. No battery overcurrent threshold is published.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Geekworm X1206 V2.0 UPS board</t>
   </si>
   <si>
-    <t xml:space="preserve">Geekworm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contradictory on the page</t>
-  </si>
-  <si>
     <t xml:space="preserve">Batteries, shipping and import duty not included. The page showed both "Only 37 items in stock" and "Out of stock". No battery-side cutoff or efficiency is published, and the listing does not confirm running with fewer than four cells fitted.</t>
   </si>
   <si>
     <t xml:space="preserve">Battery protection</t>
   </si>
   <si>
-    <t xml:space="preserve">Included in the UPS board. The maker lists battery overcurrent, overvoltage and reverse-cell protection. Not certified or independently tested here.</t>
+    <t xml:space="preserve">Included in the UPS board. The maker lists battery overcurrent, overvoltage and reverse-cell protection, with a 2.4 V over-discharge cutoff on v1.1. Not certified or independently tested here.</t>
   </si>
   <si>
     <t xml:space="preserve">Cost by cell count</t>
@@ -649,16 +772,19 @@
     <t xml:space="preserve">Refused: over the cell current limit</t>
   </si>
   <si>
-    <t xml:space="preserve">Recommended</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Starting design</t>
+    <t xml:space="preserve">Recommended, on the 2-cell X1205 board</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The maker does not confirm the 4-cell board with three cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Starting design, on the 4-cell X1206 board</t>
   </si>
   <si>
     <t xml:space="preserve">Mass per cell, g</t>
   </si>
   <si>
-    <t xml:space="preserve">Cells + board leaves out shipping, import duty, links and enclosure. The board is not confirmed to run with fewer than four cells.</t>
+    <t xml:space="preserve">Cells + board leaves out shipping, import duty, links and enclosure. Only in-stock near match found: M50LT at ₹499 from Hubtronics, a different cell we have not modelled.</t>
   </si>
   <si>
     <t xml:space="preserve">How few cells can back up a Raspberry Pi 5?</t>
@@ -775,9 +901,21 @@
     <t xml:space="preserve">What argues against two cells</t>
   </si>
   <si>
+    <t xml:space="preserve">No spare: if one cell or its contact fails, the backup fails. Three cells is the smallest design that survives losing a cell.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Less margin: 5.33 A worst case, against 3.34 A for four cells.</t>
   </si>
   <si>
+    <t xml:space="preserve">Cold rooms: below 10 °C the LG sheet limits each cell to 2.425 A, so two cells could not carry this load. The study holds 23 °C.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A bought board has a fixed cell layout, so the far-cell output needs your own wiring. The same-end layout also passes all 33 required tests.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The X1205 publishes no battery overcurrent threshold, so its limit at about 8 A must be measured.</t>
+  </si>
+  <si>
     <t xml:space="preserve">The 12 A stress test can fail: 2 of 62 mixed samples were refused. All 62 passed at the Pi load.</t>
   </si>
   <si>
@@ -787,6 +925,33 @@
     <t xml:space="preserve">Temperatures are a range, not a prediction. See Evidence.</t>
   </si>
   <si>
+    <t xml:space="preserve">If the Pi draws less than 25 W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One cell stays under its limit below, W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 W is the supply rating, not a measured draw. Published readings are about 8.8 W on a CPU stress test and up to 16 W with an SSD and video.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recharge after a 10-minute outage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charge used, Ah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charge current, A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two cells at the LG 1.455 A limit up to 25 °C. The X1205 can charge at up to 3 A, so it should be set just below that.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Time to put it back, minutes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simple estimate, before the slower finish of a real charge</t>
+  </si>
+  <si>
     <t xml:space="preserve">How far the results can be trusted</t>
   </si>
   <si>
@@ -802,10 +967,10 @@
     <t xml:space="preserve">Python tests</t>
   </si>
   <si>
-    <t xml:space="preserve">438 passed, 8 known skips</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clean install; one test added later also passes</t>
+    <t xml:space="preserve">442 passed, 8 known skips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clean install of the final code</t>
   </si>
   <si>
     <t xml:space="preserve">JavaScript tests</t>
@@ -817,6 +982,15 @@
     <t xml:space="preserve">Editor and app logic</t>
   </si>
   <si>
+    <t xml:space="preserve">AI route</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 of 4 prompts on Claude and on Codex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Each plain-English request opened an editable draft</t>
+  </si>
+  <si>
     <t xml:space="preserve">Independent solver (PyBaMM)</t>
   </si>
   <si>
@@ -865,10 +1039,10 @@
     <t xml:space="preserve">Audit of V3 findings</t>
   </si>
   <si>
-    <t xml:space="preserve">15 fixed, 3 partly, 2 open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Self-check, not independent. Open: VF3-08, VF3-19</t>
+    <t xml:space="preserve">16 fixed, 3 partly, 1 bounded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Self-check of the V3 findings. VF3-08 stays unresolved but does not change the decision. A fresh reviewer then raised 26 items on V4: see INDEPENDENT_AUDIT.md</t>
   </si>
   <si>
     <t xml:space="preserve">Compared with published measurements: frozen before any run, never used to fit</t>
@@ -961,6 +1135,174 @@
     <t xml:space="preserve">What this means: single cells heat up more than the model says, and the test rig ran cooler than it says. So cooling depends on the rig, and every temperature stays a range. Voltage also stayed outside its band.</t>
   </si>
   <si>
+    <t xml:space="preserve">Does that error change the decision? Limits frozen before running</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current share, test28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.13 points average error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5 points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current share, test53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.21 points average error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Busiest cell named, test28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62% of samples</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Busiest cell named, test53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48% of samples</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voltage error in the Pi's charge range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.17 V, model too high</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.20 V margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pass, by 0.03 V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temperature at the worst known error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.4 °C, at 2.27 times the rise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55 °C, LG sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42 A against a true 25 W load</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cell peak 4.21 A against 3.90 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Must be the harder case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OCV slope against entropy (VF3-08)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.0 °C, worst variant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55 °C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LG low-charge table change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lowest charge 54.0% across all 33 tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Above 18%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 28: share of the current in a real four-cell module, % (added after the run)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cell, from nearest the output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measured, first 10%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measured, last 10%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cell 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cell 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cell 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cell 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The model's average error is 1.13 points, against 2.38 for a guess that every cell carries 25%. The assumed sensor order fits best of all 24 possible orders. On test 53, with no added link resistance, the cells shared almost evenly and the model did no better than that guess. One module is not proof. The sensors' calibration is unresolved, and shares cancel only a gain common to all sensors. That test used 3 mΩ links, three times the design's.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real heating over the first 10 minutes, the length of the Pi job (added after the run)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measured discharge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measured rise, K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model rise, K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real over model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 28, M50T module</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test 53, M50T module</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warwick cell 2 2.5 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warwick cell 2 5 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warwick cell 3 2.5 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warwick cell 3 5 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warwick cell 4 2.5 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warwick cell 4 5 A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Highest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warwick cells are LG M50 family, not confirmed M50T. The 2.27 in the table above comes from a full discharge taken close to empty, so it is the harsher figure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtual protection: with cutoffs of 7 A a cell, 3.3 V and 45 C, with 0.5 s sensing and 0.5 s response, the design finished the job without tripping.</t>
+  </si>
+  <si>
     <t xml:space="preserve">What is assumed, untested and where each number came from</t>
   </si>
   <si>
@@ -973,19 +1315,58 @@
     <t xml:space="preserve">Nothing has been built. All results are simulated.</t>
   </si>
   <si>
-    <t xml:space="preserve">No hardware test and no real user trial. Both are the next step.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Not tested: Windows, browsers other than Chrome, the Codex AI route.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No independent audit yet.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The UPS board may not run with fewer than four cells, and publishes no cutoff or efficiency.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The LG low-charge table change is recorded as unvalidated.</t>
+    <t xml:space="preserve">No hardware test and no real user trial yet. No user has tried the app.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No accuracy figure exists: the published-data checks missed, and the sealed records stay closed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not tested: Windows.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The X1205 publishes no battery overcurrent threshold, so its limit at about 8 A is unknown.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The LG low-charge table change is unvalidated. The Pi job never reaches it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OCV slope against entropy (VF3-08) is unresolved. It does not change the decision.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not in scope for Round 1: ageing, packaging, energy management and full charge modelling.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Find the smallest design tests normal conditions only. The weak-cell tests are in the study.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salary inputs are approximate: principals use a senior-engineer average and senior physics a 3 to 5 year band.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The number of paying teams in India has not been sized.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Safety precautions for the bench test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stay low voltage: one parallel group, never above 4.2 V.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Use new, unprotected 21700 cells from one batch, as the board maker asks. Never mix old and new cells or brands.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check each cell is at the same voltage before fitting. Fit them with the board off and check polarity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keep a temperature sensor on the busiest cell and stop at 45 °C, well below the 55 °C limit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charge only between 0 and 45 °C, below 2.9 A for two cells at room temperature.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work on a non-flammable surface with someone present. Never leave a test running alone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stop and move away if a cell swells, smells or heats quickly.</t>
   </si>
   <si>
     <t xml:space="preserve">Sources</t>
@@ -1063,7 +1444,43 @@
     <t xml:space="preserve">https://www.bbelectro.net/etp-copper-busbars.html</t>
   </si>
   <si>
+    <t xml:space="preserve">https://geekworm.com/products/x1205</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://geekworm.com/products/x1206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">X1205 cutoff and efficiency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://wiki.geekworm.com/X1205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LG current and temperature limits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LG INR21700 M50T product specification, Rev 0, sections 2.7, 4.2.3 and 4.2.4. Section locators: configs/source_locators_v1.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LG M50T identity of the model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PyECN paper, Section 3.1, https://doi.org/10.31224/2972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Team plan benchmark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.mathworks.com/content/dam/mathworks/price-lists/north-america-standard.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real Pi 5 draw, about 8.8 W CPU stress and up to 16 W with SSD and video</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://raspberry.tips/en/?p=8794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Team plan, ₹5 lakh a year</t>
   </si>
   <si>
     <t xml:space="preserve">Module test data</t>
@@ -1243,7 +1660,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1388,11 +1805,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="174" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1453,6 +1870,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="177" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1782,7 +2203,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -1857,7 +2278,7 @@
         <v>12</v>
       </c>
       <c r="B9" s="9" t="n">
-        <f aca="false">Parts!C15</f>
+        <f aca="false">Parts!C16</f>
         <v>2412</v>
       </c>
       <c r="C9" s="7" t="s">
@@ -1880,9 +2301,9 @@
       <c r="A11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="6" t="n">
-        <f aca="false">Evidence!I30</f>
-        <v>0</v>
+      <c r="B11" s="10" t="n">
+        <f aca="false">Evidence!B48</f>
+        <v>33.6132097525627</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>17</v>
@@ -1893,8 +2314,8 @@
         <v>18</v>
       </c>
       <c r="B12" s="10" t="n">
-        <f aca="false">'Build cost'!B49</f>
-        <v>35.38284</v>
+        <f aca="false">Evidence!B51</f>
+        <v>18.7522415390335</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>19</v>
@@ -1904,9 +2325,9 @@
       <c r="A13" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="10" t="n">
-        <f aca="false">'Build cost'!H23</f>
-        <v>100.5</v>
+      <c r="B13" s="6" t="n">
+        <f aca="false">Evidence!I31</f>
+        <v>0</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>21</v>
@@ -1916,9 +2337,9 @@
       <c r="A14" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="11" t="n">
-        <f aca="false">'Build cost'!B68</f>
-        <v>0.0195075408401529</v>
+      <c r="B14" s="8" t="n">
+        <f aca="false">Evidence!D64</f>
+        <v>1.1341300553378</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>23</v>
@@ -1929,8 +2350,8 @@
         <v>24</v>
       </c>
       <c r="B15" s="10" t="n">
-        <f aca="false">Market!B18</f>
-        <v>41.31303</v>
+        <f aca="false">'Build cost'!B49</f>
+        <v>35.38284</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>25</v>
@@ -1941,8 +2362,8 @@
         <v>26</v>
       </c>
       <c r="B16" s="10" t="n">
-        <f aca="false">Market!B19</f>
-        <v>15.55323</v>
+        <f aca="false">'Build cost'!H23</f>
+        <v>100.5</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>27</v>
@@ -1952,63 +2373,78 @@
       <c r="A17" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="11" t="n">
+        <f aca="false">'Build cost'!B68</f>
+        <v>0.0195075408401529</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="10" t="n">
+        <f aca="false">Market!B18</f>
+        <v>41.31303</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="10" t="n">
+        <f aca="false">Market!B19</f>
+        <v>15.55323</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="6" t="n">
         <f aca="false">Market!B20</f>
         <v>130</v>
       </c>
-      <c r="C17" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="12" t="s">
+      <c r="C20" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="10" t="n">
+        <f aca="false">Market!B37</f>
+        <v>10.9713536672088</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="6" t="n">
+        <f aca="false">Market!E37</f>
         <v>31</v>
       </c>
-      <c r="B20" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="13"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C21" s="13"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C22" s="13"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" s="13"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="12" t="s">
+      <c r="C22" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="13" t="s">
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C24" s="13"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
@@ -2019,59 +2455,104 @@
       </c>
       <c r="C25" s="13"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="12" t="s">
         <v>43</v>
       </c>
+      <c r="B26" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="13"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" s="13"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="14" t="s">
-        <v>44</v>
+      <c r="A28" s="12" t="s">
+        <v>47</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C28" s="13"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="s">
-        <v>46</v>
+      <c r="A29" s="12" t="s">
+        <v>49</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="15" t="s">
-        <v>48</v>
+      <c r="A30" s="12" t="s">
+        <v>51</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C30" s="13"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C31" s="13"/>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C33" s="13"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C34" s="13"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C35" s="13"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C36" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
     <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2098,55 +2579,55 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B5" s="17" t="n">
         <v>1.4</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="B6" s="18" t="n">
         <v>0.2</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="B7" s="19" t="n">
         <v>88</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="B8" s="19" t="n">
         <v>3</v>
@@ -2154,44 +2635,44 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="C12" s="20" t="n">
         <v>37</v>
@@ -2211,10 +2692,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="C13" s="21" t="n">
         <v>0.5</v>
@@ -2246,10 +2727,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="C14" s="21" t="n">
         <v>1</v>
@@ -2281,10 +2762,10 @@
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="C15" s="21" t="n">
         <v>1</v>
@@ -2316,10 +2797,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C16" s="21" t="n">
         <v>1</v>
@@ -2351,10 +2832,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="C17" s="21" t="n">
         <v>0</v>
@@ -2386,10 +2867,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C18" s="21" t="n">
         <v>0</v>
@@ -2421,10 +2902,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C19" s="21" t="n">
         <v>0</v>
@@ -2456,10 +2937,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="C20" s="21" t="n">
         <v>0</v>
@@ -2491,10 +2972,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C21" s="21" t="n">
         <v>0</v>
@@ -2526,10 +3007,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C22" s="21" t="n">
         <v>3</v>
@@ -2561,7 +3042,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="H23" s="25" t="n">
         <f aca="false">SUM(H13:H22)</f>
@@ -2578,35 +3059,35 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="4" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="C27" s="28" t="n">
         <v>500</v>
@@ -2622,10 +3103,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="C28" s="28" t="n">
         <v>5</v>
@@ -2641,10 +3122,10 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C29" s="28" t="n">
         <v>4</v>
@@ -2660,10 +3141,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C30" s="28" t="n">
         <v>4</v>
@@ -2679,10 +3160,10 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C31" s="28" t="n">
         <v>1</v>
@@ -2698,7 +3179,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="F32" s="26" t="n">
         <f aca="false">SUM(F27:F31)</f>
@@ -2707,29 +3188,29 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C36" s="19" t="n">
         <v>30</v>
@@ -2741,10 +3222,10 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C37" s="19" t="n">
         <v>40</v>
@@ -2756,10 +3237,10 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="C38" s="19" t="n">
         <v>30</v>
@@ -2771,7 +3252,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="D39" s="31" t="n">
         <f aca="false">SUM(D36:D38)</f>
@@ -2780,10 +3261,10 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="D40" s="29" t="n">
         <v>50</v>
@@ -2791,23 +3272,23 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="B44" s="24" t="n">
         <f aca="false">I23/100</f>
@@ -2820,7 +3301,7 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B45" s="24" t="n">
         <f aca="false">F32/100</f>
@@ -2833,7 +3314,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B46" s="24" t="n">
         <f aca="false">D39/100</f>
@@ -2846,7 +3327,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="B47" s="24" t="n">
         <f aca="false">D40/100</f>
@@ -2859,7 +3340,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="B48" s="24" t="n">
         <f aca="false">SUM(B44:B47)*$B$6</f>
@@ -2872,7 +3353,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B49" s="27" t="n">
         <f aca="false">SUM(B44:B48)</f>
@@ -2885,7 +3366,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="B50" s="22" t="n">
         <f aca="false">B49*10/$B$7</f>
@@ -2894,7 +3375,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B51" s="22" t="n">
         <f aca="false">H23/$B$8</f>
@@ -2903,12 +3384,12 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="B54" s="19" t="n">
         <v>60</v>
@@ -2916,7 +3397,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="B55" s="19" t="n">
         <v>60</v>
@@ -2924,7 +3405,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B56" s="19" t="n">
         <v>20</v>
@@ -2932,7 +3413,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="B57" s="19" t="n">
         <v>30</v>
@@ -2940,7 +3421,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="B58" s="19" t="n">
         <v>10</v>
@@ -2948,7 +3429,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="B59" s="19" t="n">
         <v>20</v>
@@ -2956,7 +3437,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="B60" s="33" t="n">
         <f aca="false">SUM(B54:B59)</f>
@@ -2965,7 +3446,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="B61" s="30" t="n">
         <f aca="false">2.94*B60^1.0997</f>
@@ -2974,7 +3455,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="B62" s="24" t="n">
         <f aca="false">B61/12*I23/H23/100</f>
@@ -2983,24 +3464,24 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="B63" s="32" t="n">
         <f aca="false">B62/J23-1</f>
         <v>-0.173119578849779</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B66" s="20" t="n">
         <v>206.114</v>
@@ -3008,7 +3489,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="B67" s="30" t="n">
         <f aca="false">B66*$B$7/10</f>
@@ -3017,11 +3498,14 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="12" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="B68" s="34" t="n">
         <f aca="false">B49/B67</f>
         <v>0.0195075408401529</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -3040,43 +3524,44 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="B6" s="28" t="n">
         <v>4131303</v>
@@ -3085,7 +3570,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="B7" s="28" t="n">
         <v>605023</v>
@@ -3094,7 +3579,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="B8" s="28" t="n">
         <v>574940</v>
@@ -3103,7 +3588,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="B9" s="28" t="n">
         <v>375360</v>
@@ -3112,97 +3597,97 @@
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="B10" s="28" t="n">
         <v>2610</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="B13" s="29" t="n">
         <v>50000</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="B14" s="18" t="n">
         <v>0.05</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B18" s="25" t="n">
         <f aca="false">B6/100000</f>
         <v>41.31303</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B19" s="25" t="n">
         <f aca="false">SUM(B7:B9)/100000</f>
         <v>15.55323</v>
       </c>
       <c r="C19" s="35" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B20" s="33" t="n">
         <f aca="false">ROUNDDOWN(B10*B14,0)</f>
         <v>130</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="B21" s="22" t="n">
         <f aca="false">B20*B13/100000</f>
@@ -3211,22 +3696,220 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="B24" s="6" t="n">
         <f aca="false">'Build cost'!B49*100/B21</f>
         <v>54.4351384615385</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>167</v>
+        <v>178</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B28" s="28" t="n">
+        <v>2625</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B29" s="28" t="n">
+        <v>3965</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="B30" s="28" t="n">
+        <v>2625</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="B31" s="28" t="n">
+        <v>3965</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="B32" s="10" t="n">
+        <f aca="false">SUM(B28:B31)*'Build cost'!$B$7/100000</f>
+        <v>11.5984</v>
+      </c>
+      <c r="C32" s="35" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B33" s="29" t="n">
+        <v>500000</v>
+      </c>
+      <c r="C33" s="35" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="B34" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" s="35" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="B37" s="10" t="n">
+        <f aca="false">('Build cost'!J13+'Build cost'!J18+'Build cost'!J21+('Build cost'!F32+'Build cost'!D36)/100+('Build cost'!D39-'Build cost'!D36+'Build cost'!D40)/100*('Build cost'!J13+'Build cost'!J18+'Build cost'!J21)/'Build cost'!J23)*(1+'Build cost'!$B$6)</f>
+        <v>10.9713536672088</v>
+      </c>
+      <c r="C37" s="35" t="s">
+        <v>197</v>
+      </c>
+      <c r="D37" s="22" t="n">
+        <f aca="false">SUM(B$37:B37)</f>
+        <v>10.9713536672088</v>
+      </c>
+      <c r="E37" s="36" t="n">
+        <f aca="false">ROUNDUP(MAX(0,(D37*100/$B$34-$B$21)*100000/$B$33),0)</f>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="B38" s="10" t="n">
+        <f aca="false">('Build cost'!J14+'Build cost'!J17+'Build cost'!J19+'Build cost'!J20+0+('Build cost'!D39-'Build cost'!D36+'Build cost'!D40)/100*('Build cost'!J14+'Build cost'!J17+'Build cost'!J19+'Build cost'!J20)/'Build cost'!J23)*(1+'Build cost'!$B$6)</f>
+        <v>10.6735328540183</v>
+      </c>
+      <c r="C38" s="35" t="s">
+        <v>199</v>
+      </c>
+      <c r="D38" s="22" t="n">
+        <f aca="false">SUM(B$37:B38)</f>
+        <v>21.6448865212271</v>
+      </c>
+      <c r="E38" s="36" t="n">
+        <f aca="false">ROUNDUP(MAX(0,(D38*100/$B$34-$B$21)*100000/$B$33),0)</f>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="B39" s="10" t="n">
+        <f aca="false">('Build cost'!J15+'Build cost'!J16+'Build cost'!J22+0+('Build cost'!D39-'Build cost'!D36+'Build cost'!D40)/100*('Build cost'!J15+'Build cost'!J16+'Build cost'!J22)/'Build cost'!J23)*(1+'Build cost'!$B$6)</f>
+        <v>13.7379534787729</v>
+      </c>
+      <c r="C39" s="35" t="s">
+        <v>201</v>
+      </c>
+      <c r="D39" s="22" t="n">
+        <f aca="false">SUM(B$37:B39)</f>
+        <v>35.38284</v>
+      </c>
+      <c r="E39" s="36" t="n">
+        <f aca="false">ROUNDUP(MAX(0,(D39*100/$B$34-$B$21)*100000/$B$33),0)</f>
+        <v>129</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="B42" s="22" t="n">
+        <f aca="false">B37/B34</f>
+        <v>2.19427073344176</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="B43" s="36" t="n">
+        <f aca="false">ROUNDUP(B37*10000000/B34/B33,0)</f>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B44" s="36" t="n">
+        <f aca="false">ROUNDUP(B37*10000000/B34/B13,0)</f>
+        <v>439</v>
+      </c>
+      <c r="C44" s="35" t="s">
+        <v>206</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="A40:E40"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -3242,7 +3925,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -3256,302 +3939,327 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>168</v>
+        <v>207</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>169</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>170</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>171</v>
+        <v>210</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>172</v>
+        <v>211</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>173</v>
+        <v>212</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>174</v>
+        <v>213</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>175</v>
+        <v>214</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>176</v>
+        <v>215</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>177</v>
+        <v>216</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="C6" s="36" t="n">
+        <v>217</v>
+      </c>
+      <c r="C6" s="37" t="n">
         <v>1206</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>179</v>
+        <v>218</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>180</v>
+        <v>219</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>181</v>
+        <v>220</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>182</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>183</v>
+        <v>222</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="C7" s="36" t="n">
+        <v>223</v>
+      </c>
+      <c r="C7" s="37" t="n">
         <v>6.99</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>185</v>
+        <v>224</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>187</v>
+        <v>226</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>188</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>189</v>
+        <v>228</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="C8" s="36" t="n">
+        <v>229</v>
+      </c>
+      <c r="C8" s="37" t="n">
         <v>920</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>179</v>
+        <v>218</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>191</v>
+        <v>230</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>192</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>193</v>
+        <v>232</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="C9" s="36" t="n">
+        <v>233</v>
+      </c>
+      <c r="C9" s="37" t="n">
+        <v>46</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="C10" s="37" t="n">
         <v>52</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
-        <v>197</v>
+      <c r="D10" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>234</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
-        <v>199</v>
+        <v>237</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>146</v>
+      <c r="A13" s="3" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="37" t="n">
+      <c r="A14" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="B14" s="37" t="n">
-        <f aca="false">A14*$B$18</f>
+      <c r="B15" s="36" t="n">
+        <f aca="false">A15*$B$19</f>
         <v>70</v>
       </c>
-      <c r="C14" s="30" t="n">
-        <f aca="false">A14*$C$6</f>
+      <c r="C15" s="30" t="n">
+        <f aca="false">A15*$C$6</f>
         <v>1206</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D15" s="9" t="n">
+        <f aca="false">$C$10*'Build cost'!$B$7</f>
+        <v>4576</v>
+      </c>
+      <c r="E15" s="30" t="n">
+        <f aca="false">C15+D15</f>
+        <v>5782</v>
+      </c>
+      <c r="F15" s="32" t="n">
+        <f aca="false">1-E15/$E$18</f>
+        <v>0.384893617021277</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="39" t="n">
+        <f aca="false">A16*$B$19</f>
+        <v>140</v>
+      </c>
+      <c r="C16" s="40" t="n">
+        <f aca="false">A16*$C$6</f>
+        <v>2412</v>
+      </c>
+      <c r="D16" s="41" t="n">
         <f aca="false">$C$9*'Build cost'!$B$7</f>
-        <v>4576</v>
-      </c>
-      <c r="E14" s="30" t="n">
-        <f aca="false">C14+D14</f>
-        <v>5782</v>
-      </c>
-      <c r="F14" s="32" t="n">
-        <f aca="false">1-E14/$E$17</f>
-        <v>0.384893617021277</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="38" t="n">
-        <v>2</v>
-      </c>
-      <c r="B15" s="39" t="n">
-        <f aca="false">A15*$B$18</f>
-        <v>140</v>
-      </c>
-      <c r="C15" s="40" t="n">
-        <f aca="false">A15*$C$6</f>
-        <v>2412</v>
-      </c>
-      <c r="D15" s="41" t="n">
-        <f aca="false">$C$9*'Build cost'!$B$7</f>
-        <v>4576</v>
-      </c>
-      <c r="E15" s="40" t="n">
-        <f aca="false">C15+D15</f>
-        <v>6988</v>
-      </c>
-      <c r="F15" s="42" t="n">
-        <f aca="false">1-E15/$E$17</f>
-        <v>0.256595744680851</v>
-      </c>
-      <c r="G15" s="43" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="37" t="n">
+        <v>4048</v>
+      </c>
+      <c r="E16" s="40" t="n">
+        <f aca="false">C16+D16</f>
+        <v>6460</v>
+      </c>
+      <c r="F16" s="42" t="n">
+        <f aca="false">1-E16/$E$18</f>
+        <v>0.312765957446808</v>
+      </c>
+      <c r="G16" s="43" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="B16" s="37" t="n">
-        <f aca="false">A16*$B$18</f>
+      <c r="B17" s="36" t="n">
+        <f aca="false">A17*$B$19</f>
         <v>210</v>
-      </c>
-      <c r="C16" s="30" t="n">
-        <f aca="false">A16*$C$6</f>
-        <v>3618</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <f aca="false">$C$9*'Build cost'!$B$7</f>
-        <v>4576</v>
-      </c>
-      <c r="E16" s="30" t="n">
-        <f aca="false">C16+D16</f>
-        <v>8194</v>
-      </c>
-      <c r="F16" s="32" t="n">
-        <f aca="false">1-E16/$E$17</f>
-        <v>0.128297872340426</v>
-      </c>
-      <c r="G16" s="5"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="37" t="n">
-        <v>4</v>
-      </c>
-      <c r="B17" s="37" t="n">
-        <f aca="false">A17*$B$18</f>
-        <v>280</v>
       </c>
       <c r="C17" s="30" t="n">
         <f aca="false">A17*$C$6</f>
-        <v>4824</v>
+        <v>3618</v>
       </c>
       <c r="D17" s="9" t="n">
-        <f aca="false">$C$9*'Build cost'!$B$7</f>
+        <f aca="false">$C$10*'Build cost'!$B$7</f>
         <v>4576</v>
       </c>
       <c r="E17" s="30" t="n">
         <f aca="false">C17+D17</f>
+        <v>8194</v>
+      </c>
+      <c r="F17" s="32" t="n">
+        <f aca="false">1-E17/$E$18</f>
+        <v>0.128297872340426</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="B18" s="36" t="n">
+        <f aca="false">A18*$B$19</f>
+        <v>280</v>
+      </c>
+      <c r="C18" s="30" t="n">
+        <f aca="false">A18*$C$6</f>
+        <v>4824</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <f aca="false">$C$10*'Build cost'!$B$7</f>
+        <v>4576</v>
+      </c>
+      <c r="E18" s="30" t="n">
+        <f aca="false">C18+D18</f>
         <v>9400</v>
       </c>
-      <c r="F17" s="32" t="n">
-        <f aca="false">1-E17/$E$17</f>
+      <c r="F18" s="32" t="n">
+        <f aca="false">1-E18/$E$18</f>
         <v>0</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="B18" s="44" t="n">
+      <c r="G18" s="5" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B19" s="44" t="n">
         <v>70</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="s">
-        <v>210</v>
-      </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A20:G20"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3568,7 +4276,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -3580,22 +4288,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>211</v>
+        <v>253</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>212</v>
+        <v>254</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>213</v>
+        <v>255</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>214</v>
+        <v>256</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="44" t="n">
@@ -3604,7 +4312,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>215</v>
+        <v>257</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="18" t="n">
@@ -3613,7 +4321,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>216</v>
+        <v>258</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="45" t="n">
@@ -3622,7 +4330,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>217</v>
+        <v>259</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="46" t="n">
@@ -3631,7 +4339,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>218</v>
+        <v>260</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="24" t="n">
@@ -3639,83 +4347,83 @@
         <v>8.41750841750842</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>219</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>220</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>200</v>
+        <v>241</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>221</v>
+        <v>263</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>222</v>
+        <v>264</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>223</v>
+        <v>265</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>224</v>
+        <v>266</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>225</v>
+        <v>267</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>226</v>
+        <v>268</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>227</v>
+        <v>269</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>229</v>
+        <v>271</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>230</v>
+        <v>272</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>231</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="37" t="n">
+      <c r="A13" s="36" t="n">
         <v>1</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>232</v>
+        <v>274</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="D13" s="37" t="n">
+        <v>275</v>
+      </c>
+      <c r="D13" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="37" t="n">
+      <c r="E13" s="36" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="37" t="n">
+      <c r="A14" s="36" t="n">
         <v>2</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>232</v>
+        <v>274</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="D14" s="37" t="n">
+        <v>276</v>
+      </c>
+      <c r="D14" s="36" t="n">
         <v>33</v>
       </c>
-      <c r="E14" s="37" t="n">
+      <c r="E14" s="36" t="n">
         <v>33</v>
       </c>
       <c r="F14" s="24" t="n">
@@ -3738,23 +4446,23 @@
         <v>1.78964096228307</v>
       </c>
       <c r="L14" s="47" t="s">
-        <v>235</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="37" t="n">
+      <c r="A15" s="36" t="n">
         <v>2</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>236</v>
+        <v>278</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="D15" s="37" t="n">
+        <v>276</v>
+      </c>
+      <c r="D15" s="36" t="n">
         <v>33</v>
       </c>
-      <c r="E15" s="37" t="n">
+      <c r="E15" s="36" t="n">
         <v>33</v>
       </c>
       <c r="F15" s="24" t="n">
@@ -3777,7 +4485,7 @@
         <v>1.92961507873691</v>
       </c>
       <c r="L15" s="47" t="s">
-        <v>237</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3785,10 +4493,10 @@
         <v>2</v>
       </c>
       <c r="B16" s="43" t="s">
-        <v>238</v>
+        <v>280</v>
       </c>
       <c r="C16" s="43" t="s">
-        <v>234</v>
+        <v>276</v>
       </c>
       <c r="D16" s="39" t="n">
         <v>33</v>
@@ -3816,23 +4524,23 @@
         <v>1.94657449562736</v>
       </c>
       <c r="L16" s="50" t="s">
-        <v>237</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="37" t="n">
+      <c r="A17" s="36" t="n">
         <v>2</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>239</v>
+        <v>281</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="D17" s="37" t="n">
+        <v>276</v>
+      </c>
+      <c r="D17" s="36" t="n">
         <v>33</v>
       </c>
-      <c r="E17" s="37" t="n">
+      <c r="E17" s="36" t="n">
         <v>33</v>
       </c>
       <c r="F17" s="24" t="n">
@@ -3855,23 +4563,23 @@
         <v>1.83405358937421</v>
       </c>
       <c r="L17" s="47" t="s">
-        <v>235</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="37" t="n">
+      <c r="A18" s="36" t="n">
         <v>3</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>232</v>
+        <v>274</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="D18" s="37" t="n">
+        <v>276</v>
+      </c>
+      <c r="D18" s="36" t="n">
         <v>42</v>
       </c>
-      <c r="E18" s="37" t="n">
+      <c r="E18" s="36" t="n">
         <v>42</v>
       </c>
       <c r="F18" s="24" t="n">
@@ -3894,23 +4602,23 @@
         <v>3.41951962163663</v>
       </c>
       <c r="L18" s="47" t="s">
-        <v>240</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="37" t="n">
+      <c r="A19" s="36" t="n">
         <v>3</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>236</v>
+        <v>278</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="D19" s="37" t="n">
+        <v>276</v>
+      </c>
+      <c r="D19" s="36" t="n">
         <v>42</v>
       </c>
-      <c r="E19" s="37" t="n">
+      <c r="E19" s="36" t="n">
         <v>42</v>
       </c>
       <c r="F19" s="24" t="n">
@@ -3933,23 +4641,23 @@
         <v>3.74403769376495</v>
       </c>
       <c r="L19" s="47" t="s">
-        <v>240</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="37" t="n">
+      <c r="A20" s="36" t="n">
         <v>3</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>238</v>
+        <v>280</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="D20" s="37" t="n">
+        <v>276</v>
+      </c>
+      <c r="D20" s="36" t="n">
         <v>42</v>
       </c>
-      <c r="E20" s="37" t="n">
+      <c r="E20" s="36" t="n">
         <v>42</v>
       </c>
       <c r="F20" s="24" t="n">
@@ -3972,23 +4680,23 @@
         <v>3.73732329471304</v>
       </c>
       <c r="L20" s="47" t="s">
-        <v>240</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="37" t="n">
+      <c r="A21" s="36" t="n">
         <v>3</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>239</v>
+        <v>281</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="D21" s="37" t="n">
+        <v>276</v>
+      </c>
+      <c r="D21" s="36" t="n">
         <v>42</v>
       </c>
-      <c r="E21" s="37" t="n">
+      <c r="E21" s="36" t="n">
         <v>42</v>
       </c>
       <c r="F21" s="24" t="n">
@@ -4011,23 +4719,23 @@
         <v>3.54746547431914</v>
       </c>
       <c r="L21" s="47" t="s">
-        <v>240</v>
+        <v>282</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="37" t="n">
+      <c r="A22" s="36" t="n">
         <v>4</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>232</v>
+        <v>274</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="D22" s="37" t="n">
+        <v>276</v>
+      </c>
+      <c r="D22" s="36" t="n">
         <v>51</v>
       </c>
-      <c r="E22" s="37" t="n">
+      <c r="E22" s="36" t="n">
         <v>51</v>
       </c>
       <c r="F22" s="24" t="n">
@@ -4050,23 +4758,23 @@
         <v>3.93449868621807</v>
       </c>
       <c r="L22" s="47" t="s">
-        <v>241</v>
+        <v>283</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="37" t="n">
+      <c r="A23" s="36" t="n">
         <v>4</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>236</v>
+        <v>278</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="D23" s="37" t="n">
+        <v>276</v>
+      </c>
+      <c r="D23" s="36" t="n">
         <v>51</v>
       </c>
-      <c r="E23" s="37" t="n">
+      <c r="E23" s="36" t="n">
         <v>51</v>
       </c>
       <c r="F23" s="24" t="n">
@@ -4089,23 +4797,23 @@
         <v>4.3964989640048</v>
       </c>
       <c r="L23" s="47" t="s">
-        <v>241</v>
+        <v>283</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="37" t="n">
+      <c r="A24" s="36" t="n">
         <v>4</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>238</v>
+        <v>280</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="D24" s="37" t="n">
+        <v>276</v>
+      </c>
+      <c r="D24" s="36" t="n">
         <v>51</v>
       </c>
-      <c r="E24" s="37" t="n">
+      <c r="E24" s="36" t="n">
         <v>51</v>
       </c>
       <c r="F24" s="24" t="n">
@@ -4128,23 +4836,23 @@
         <v>4.38850110361279</v>
       </c>
       <c r="L24" s="47" t="s">
-        <v>241</v>
+        <v>283</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="37" t="n">
+      <c r="A25" s="36" t="n">
         <v>4</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>239</v>
+        <v>281</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="D25" s="37" t="n">
+        <v>276</v>
+      </c>
+      <c r="D25" s="36" t="n">
         <v>51</v>
       </c>
-      <c r="E25" s="37" t="n">
+      <c r="E25" s="36" t="n">
         <v>51</v>
       </c>
       <c r="F25" s="24" t="n">
@@ -4167,17 +4875,17 @@
         <v>4.11050972050215</v>
       </c>
       <c r="L25" s="47" t="s">
-        <v>241</v>
+        <v>283</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>242</v>
+        <v>284</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>243</v>
+        <v>285</v>
       </c>
       <c r="B28" s="13"/>
       <c r="C28" s="13"/>
@@ -4192,7 +4900,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>244</v>
+        <v>286</v>
       </c>
       <c r="B29" s="13"/>
       <c r="C29" s="13"/>
@@ -4201,13 +4909,13 @@
       <c r="F29" s="13"/>
       <c r="G29" s="13"/>
       <c r="H29" s="13"/>
-      <c r="I29" s="37" t="n">
+      <c r="I29" s="36" t="n">
         <v>42</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>245</v>
+        <v>287</v>
       </c>
       <c r="B30" s="13"/>
       <c r="C30" s="13"/>
@@ -4223,7 +4931,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>246</v>
+        <v>288</v>
       </c>
       <c r="B31" s="13"/>
       <c r="C31" s="13"/>
@@ -4238,7 +4946,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>247</v>
+        <v>289</v>
       </c>
       <c r="B32" s="13"/>
       <c r="C32" s="13"/>
@@ -4253,12 +4961,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>248</v>
+        <v>290</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="13" t="s">
-        <v>249</v>
+        <v>291</v>
       </c>
       <c r="B35" s="13"/>
       <c r="C35" s="13"/>
@@ -4274,7 +4982,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>250</v>
+        <v>292</v>
       </c>
       <c r="B36" s="13"/>
       <c r="C36" s="13"/>
@@ -4290,7 +4998,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>251</v>
+        <v>293</v>
       </c>
       <c r="B37" s="13"/>
       <c r="C37" s="13"/>
@@ -4306,7 +5014,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="13" t="s">
-        <v>252</v>
+        <v>294</v>
       </c>
       <c r="B38" s="13"/>
       <c r="C38" s="13"/>
@@ -4320,8 +5028,130 @@
       <c r="K38" s="13"/>
       <c r="L38" s="13"/>
     </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="13" t="s">
+        <v>295</v>
+      </c>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="13"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="13"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13"/>
+      <c r="J40" s="13"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="13"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="13"/>
+      <c r="J41" s="13"/>
+      <c r="K41" s="13"/>
+      <c r="L41" s="13"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="I42" s="13"/>
+      <c r="J42" s="13"/>
+      <c r="K42" s="13"/>
+      <c r="L42" s="13"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="3" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="B45" s="13"/>
+      <c r="C45" s="22" t="n">
+        <f aca="false">$C$8*$C$7*$C$6</f>
+        <v>21.60675</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="13" t="s">
+        <v>303</v>
+      </c>
+      <c r="B48" s="13"/>
+      <c r="C48" s="22" t="n">
+        <f aca="false">$C$5/$C$6/$C$7*10/60</f>
+        <v>1.40291806958474</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="B49" s="13"/>
+      <c r="C49" s="53" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="B50" s="13"/>
+      <c r="C50" s="36" t="n">
+        <f aca="false">C48/C49*60</f>
+        <v>28.9261457646337</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>307</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="22">
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A7:B7"/>
@@ -4336,6 +5166,14 @@
     <mergeCell ref="A36:L36"/>
     <mergeCell ref="A37:L37"/>
     <mergeCell ref="A38:L38"/>
+    <mergeCell ref="A39:L39"/>
+    <mergeCell ref="A40:L40"/>
+    <mergeCell ref="A41:L41"/>
+    <mergeCell ref="A42:L42"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4352,57 +5190,58 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>253</v>
+        <v>308</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>254</v>
+        <v>309</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>255</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>256</v>
+        <v>311</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="C5" s="53" t="s">
+        <v>169</v>
+      </c>
+      <c r="C5" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="53"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>257</v>
+        <v>312</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>258</v>
+        <v>313</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>259</v>
+        <v>314</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
@@ -4414,13 +5253,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>260</v>
+        <v>315</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>261</v>
+        <v>316</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>262</v>
+        <v>317</v>
       </c>
       <c r="D7" s="13"/>
       <c r="E7" s="13"/>
@@ -4432,13 +5271,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>263</v>
+        <v>318</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>264</v>
+        <v>319</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>265</v>
+        <v>320</v>
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="13"/>
@@ -4450,13 +5289,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>266</v>
+        <v>321</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>267</v>
+        <v>322</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>268</v>
+        <v>323</v>
       </c>
       <c r="D9" s="13"/>
       <c r="E9" s="13"/>
@@ -4468,13 +5307,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>269</v>
+        <v>324</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>270</v>
+        <v>325</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>271</v>
+        <v>326</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="13"/>
@@ -4486,13 +5325,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>272</v>
+        <v>327</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>273</v>
+        <v>328</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>274</v>
+        <v>329</v>
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
@@ -4504,13 +5343,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>275</v>
+        <v>330</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>276</v>
+        <v>331</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>277</v>
+        <v>332</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="13"/>
@@ -4522,13 +5361,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>278</v>
+        <v>333</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>279</v>
+        <v>334</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>280</v>
+        <v>335</v>
       </c>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
@@ -4538,482 +5377,985 @@
       <c r="I13" s="13"/>
       <c r="J13" s="13"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
-        <v>282</v>
-      </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-    </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="C18" s="22" t="n">
-        <v>14.5610257874836</v>
-      </c>
-      <c r="D18" s="54" t="n">
-        <v>0.180389649105501</v>
-      </c>
-      <c r="E18" s="24" t="n">
-        <v>3.03017384353483</v>
-      </c>
-      <c r="F18" s="24" t="n">
-        <v>5.33761537365797</v>
-      </c>
-      <c r="G18" s="24" t="n">
-        <v>8.39682411288896</v>
-      </c>
-      <c r="H18" s="55" t="n">
-        <f aca="false">G18-F18</f>
-        <v>3.05920873923099</v>
-      </c>
-      <c r="I18" s="56" t="s">
-        <v>295</v>
-      </c>
-      <c r="J18" s="56" t="s">
-        <v>295</v>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+    </row>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>296</v>
+        <v>351</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>294</v>
+        <v>352</v>
       </c>
       <c r="C19" s="22" t="n">
-        <v>16.1089494383413</v>
-      </c>
-      <c r="D19" s="54" t="n">
-        <v>0.0802234571732305</v>
+        <v>14.5610257874836</v>
+      </c>
+      <c r="D19" s="55" t="n">
+        <v>0.180389649105501</v>
       </c>
       <c r="E19" s="24" t="n">
-        <v>4.09235171152956</v>
+        <v>3.03017384353483</v>
       </c>
       <c r="F19" s="24" t="n">
-        <v>5.10981750488281</v>
+        <v>5.33761537365797</v>
       </c>
       <c r="G19" s="24" t="n">
-        <v>9.86131154024901</v>
-      </c>
-      <c r="H19" s="55" t="n">
+        <v>8.39682411288896</v>
+      </c>
+      <c r="H19" s="56" t="n">
         <f aca="false">G19-F19</f>
-        <v>4.75149403536619</v>
-      </c>
-      <c r="I19" s="56" t="s">
-        <v>295</v>
-      </c>
-      <c r="J19" s="56" t="s">
-        <v>295</v>
+        <v>3.05920873923099</v>
+      </c>
+      <c r="I19" s="57" t="s">
+        <v>353</v>
+      </c>
+      <c r="J19" s="57" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>297</v>
+        <v>354</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>294</v>
+        <v>352</v>
       </c>
       <c r="C20" s="22" t="n">
-        <v>14.5610257874836</v>
-      </c>
-      <c r="D20" s="54" t="n">
-        <v>0.154935147845536</v>
+        <v>16.1089494383413</v>
+      </c>
+      <c r="D20" s="55" t="n">
+        <v>0.0802234571732305</v>
       </c>
       <c r="E20" s="24" t="n">
-        <v>3.32956708735821</v>
+        <v>4.09235171152956</v>
       </c>
       <c r="F20" s="24" t="n">
-        <v>5.33761537365797</v>
+        <v>5.10981750488281</v>
       </c>
       <c r="G20" s="24" t="n">
-        <v>9.04485923162991</v>
-      </c>
-      <c r="H20" s="55" t="n">
+        <v>9.86131154024901</v>
+      </c>
+      <c r="H20" s="56" t="n">
         <f aca="false">G20-F20</f>
-        <v>3.70724385797194</v>
-      </c>
-      <c r="I20" s="56" t="s">
-        <v>295</v>
-      </c>
-      <c r="J20" s="56" t="s">
-        <v>295</v>
+        <v>4.75149403536619</v>
+      </c>
+      <c r="I20" s="57" t="s">
+        <v>353</v>
+      </c>
+      <c r="J20" s="57" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>298</v>
+        <v>355</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>299</v>
+        <v>352</v>
       </c>
       <c r="C21" s="22" t="n">
-        <v>14.554388214364</v>
-      </c>
-      <c r="D21" s="54" t="n">
-        <v>0.172918467073328</v>
+        <v>14.5610257874836</v>
+      </c>
+      <c r="D21" s="55" t="n">
+        <v>0.154935147845536</v>
       </c>
       <c r="E21" s="24" t="n">
-        <v>3.25804688552848</v>
+        <v>3.32956708735821</v>
       </c>
       <c r="F21" s="24" t="n">
-        <v>2.21429298502703</v>
+        <v>5.33761537365797</v>
       </c>
       <c r="G21" s="24" t="n">
-        <v>5.8297424731429</v>
-      </c>
-      <c r="H21" s="55" t="n">
+        <v>9.04485923162991</v>
+      </c>
+      <c r="H21" s="56" t="n">
         <f aca="false">G21-F21</f>
-        <v>3.61544948811587</v>
-      </c>
-      <c r="I21" s="56" t="s">
-        <v>295</v>
-      </c>
-      <c r="J21" s="56" t="s">
-        <v>295</v>
+        <v>3.70724385797194</v>
+      </c>
+      <c r="I21" s="57" t="s">
+        <v>353</v>
+      </c>
+      <c r="J21" s="57" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>300</v>
+        <v>356</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>299</v>
+        <v>357</v>
       </c>
       <c r="C22" s="22" t="n">
-        <v>12.871096682301</v>
-      </c>
-      <c r="D22" s="54" t="n">
-        <v>0.0520087683166525</v>
+        <v>14.554388214364</v>
+      </c>
+      <c r="D22" s="55" t="n">
+        <v>0.172918467073328</v>
       </c>
       <c r="E22" s="24" t="n">
-        <v>2.35568572956209</v>
+        <v>3.25804688552848</v>
       </c>
       <c r="F22" s="24" t="n">
-        <v>3.0483614005696</v>
+        <v>2.21429298502703</v>
       </c>
       <c r="G22" s="24" t="n">
-        <v>4.86371535216071</v>
-      </c>
-      <c r="H22" s="55" t="n">
+        <v>5.8297424731429</v>
+      </c>
+      <c r="H22" s="56" t="n">
         <f aca="false">G22-F22</f>
-        <v>1.81535395159112</v>
-      </c>
-      <c r="I22" s="56" t="s">
-        <v>295</v>
-      </c>
-      <c r="J22" s="56" t="s">
-        <v>295</v>
+        <v>3.61544948811587</v>
+      </c>
+      <c r="I22" s="57" t="s">
+        <v>353</v>
+      </c>
+      <c r="J22" s="57" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>301</v>
+        <v>358</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>299</v>
+        <v>357</v>
       </c>
       <c r="C23" s="22" t="n">
-        <v>14.554388214364</v>
-      </c>
-      <c r="D23" s="54" t="n">
-        <v>0.185718294763102</v>
+        <v>12.871096682301</v>
+      </c>
+      <c r="D23" s="55" t="n">
+        <v>0.0520087683166525</v>
       </c>
       <c r="E23" s="24" t="n">
-        <v>3.55052821717712</v>
+        <v>2.35568572956209</v>
       </c>
       <c r="F23" s="24" t="n">
-        <v>2.19935774547927</v>
+        <v>3.0483614005696</v>
       </c>
       <c r="G23" s="24" t="n">
-        <v>6.58308610270481</v>
-      </c>
-      <c r="H23" s="55" t="n">
+        <v>4.86371535216071</v>
+      </c>
+      <c r="H23" s="56" t="n">
         <f aca="false">G23-F23</f>
-        <v>4.38372835722554</v>
-      </c>
-      <c r="I23" s="56" t="s">
-        <v>295</v>
-      </c>
-      <c r="J23" s="56" t="s">
-        <v>295</v>
+        <v>1.81535395159112</v>
+      </c>
+      <c r="I23" s="57" t="s">
+        <v>353</v>
+      </c>
+      <c r="J23" s="57" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>302</v>
+        <v>359</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>303</v>
+        <v>357</v>
       </c>
       <c r="C24" s="22" t="n">
-        <v>2.4999939084507</v>
-      </c>
-      <c r="D24" s="54" t="n">
-        <v>0.0679898281832401</v>
+        <v>14.554388214364</v>
+      </c>
+      <c r="D24" s="55" t="n">
+        <v>0.185718294763102</v>
       </c>
       <c r="E24" s="24" t="n">
-        <v>2.0894019505828</v>
+        <v>3.55052821717712</v>
       </c>
       <c r="F24" s="24" t="n">
-        <v>6.473</v>
+        <v>2.19935774547927</v>
       </c>
       <c r="G24" s="24" t="n">
-        <v>2.89865003734743</v>
-      </c>
-      <c r="H24" s="55" t="n">
+        <v>6.58308610270481</v>
+      </c>
+      <c r="H24" s="56" t="n">
         <f aca="false">G24-F24</f>
-        <v>-3.57434996265257</v>
-      </c>
-      <c r="I24" s="56" t="s">
-        <v>295</v>
-      </c>
-      <c r="J24" s="56" t="s">
-        <v>295</v>
+        <v>4.38372835722554</v>
+      </c>
+      <c r="I24" s="57" t="s">
+        <v>353</v>
+      </c>
+      <c r="J24" s="57" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>304</v>
+        <v>360</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>303</v>
+        <v>361</v>
       </c>
       <c r="C25" s="22" t="n">
-        <v>5.00001573863636</v>
-      </c>
-      <c r="D25" s="54" t="n">
-        <v>0.0934511292201811</v>
+        <v>2.4999939084507</v>
+      </c>
+      <c r="D25" s="55" t="n">
+        <v>0.0679898281832401</v>
       </c>
       <c r="E25" s="24" t="n">
-        <v>4.24459369804256</v>
+        <v>2.0894019505828</v>
       </c>
       <c r="F25" s="24" t="n">
-        <v>15.8462</v>
+        <v>6.473</v>
       </c>
       <c r="G25" s="24" t="n">
-        <v>9.25478037762063</v>
-      </c>
-      <c r="H25" s="55" t="n">
+        <v>2.89865003734743</v>
+      </c>
+      <c r="H25" s="56" t="n">
         <f aca="false">G25-F25</f>
-        <v>-6.59141962237937</v>
-      </c>
-      <c r="I25" s="56" t="s">
-        <v>295</v>
-      </c>
-      <c r="J25" s="56" t="s">
-        <v>295</v>
+        <v>-3.57434996265257</v>
+      </c>
+      <c r="I25" s="57" t="s">
+        <v>353</v>
+      </c>
+      <c r="J25" s="57" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>305</v>
+        <v>362</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>303</v>
+        <v>361</v>
       </c>
       <c r="C26" s="22" t="n">
-        <v>2.49997468309859</v>
-      </c>
-      <c r="D26" s="54" t="n">
-        <v>0.0704727288793828</v>
+        <v>5.00001573863636</v>
+      </c>
+      <c r="D26" s="55" t="n">
+        <v>0.0934511292201811</v>
       </c>
       <c r="E26" s="24" t="n">
-        <v>1.39750266513812</v>
+        <v>4.24459369804256</v>
       </c>
       <c r="F26" s="24" t="n">
-        <v>5.8234</v>
+        <v>15.8462</v>
       </c>
       <c r="G26" s="24" t="n">
-        <v>3.34147334344955</v>
-      </c>
-      <c r="H26" s="55" t="n">
+        <v>9.25478037762063</v>
+      </c>
+      <c r="H26" s="56" t="n">
         <f aca="false">G26-F26</f>
-        <v>-2.48192665655045</v>
-      </c>
-      <c r="I26" s="56" t="s">
-        <v>295</v>
-      </c>
-      <c r="J26" s="56" t="s">
-        <v>295</v>
+        <v>-6.59141962237937</v>
+      </c>
+      <c r="I26" s="57" t="s">
+        <v>353</v>
+      </c>
+      <c r="J26" s="57" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>306</v>
+        <v>363</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>303</v>
+        <v>361</v>
       </c>
       <c r="C27" s="22" t="n">
-        <v>5.00003897727273</v>
-      </c>
-      <c r="D27" s="54" t="n">
-        <v>0.0976914488142504</v>
+        <v>2.49997468309859</v>
+      </c>
+      <c r="D27" s="55" t="n">
+        <v>0.0704727288793828</v>
       </c>
       <c r="E27" s="24" t="n">
-        <v>3.0896831144881</v>
+        <v>1.39750266513812</v>
       </c>
       <c r="F27" s="24" t="n">
-        <v>14.6949</v>
+        <v>5.8234</v>
       </c>
       <c r="G27" s="24" t="n">
-        <v>9.76342624689893</v>
-      </c>
-      <c r="H27" s="55" t="n">
+        <v>3.34147334344955</v>
+      </c>
+      <c r="H27" s="56" t="n">
         <f aca="false">G27-F27</f>
-        <v>-4.93147375310107</v>
-      </c>
-      <c r="I27" s="56" t="s">
-        <v>295</v>
-      </c>
-      <c r="J27" s="56" t="s">
-        <v>295</v>
+        <v>-2.48192665655045</v>
+      </c>
+      <c r="I27" s="57" t="s">
+        <v>353</v>
+      </c>
+      <c r="J27" s="57" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>307</v>
+        <v>364</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>303</v>
+        <v>361</v>
       </c>
       <c r="C28" s="22" t="n">
-        <v>2.49998323943662</v>
-      </c>
-      <c r="D28" s="54" t="n">
-        <v>0.0707348376443114</v>
+        <v>5.00003897727273</v>
+      </c>
+      <c r="D28" s="55" t="n">
+        <v>0.0976914488142504</v>
       </c>
       <c r="E28" s="24" t="n">
-        <v>2.33571411735071</v>
+        <v>3.0896831144881</v>
       </c>
       <c r="F28" s="24" t="n">
-        <v>7.5322</v>
+        <v>14.6949</v>
       </c>
       <c r="G28" s="24" t="n">
-        <v>3.32084254288629</v>
-      </c>
-      <c r="H28" s="55" t="n">
+        <v>9.76342624689893</v>
+      </c>
+      <c r="H28" s="56" t="n">
         <f aca="false">G28-F28</f>
-        <v>-4.21135745711371</v>
-      </c>
-      <c r="I28" s="56" t="s">
-        <v>295</v>
-      </c>
-      <c r="J28" s="56" t="s">
-        <v>295</v>
+        <v>-4.93147375310107</v>
+      </c>
+      <c r="I28" s="57" t="s">
+        <v>353</v>
+      </c>
+      <c r="J28" s="57" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>308</v>
+        <v>365</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>303</v>
+        <v>361</v>
       </c>
       <c r="C29" s="22" t="n">
+        <v>2.49998323943662</v>
+      </c>
+      <c r="D29" s="55" t="n">
+        <v>0.0707348376443114</v>
+      </c>
+      <c r="E29" s="24" t="n">
+        <v>2.33571411735071</v>
+      </c>
+      <c r="F29" s="24" t="n">
+        <v>7.5322</v>
+      </c>
+      <c r="G29" s="24" t="n">
+        <v>3.32084254288629</v>
+      </c>
+      <c r="H29" s="56" t="n">
+        <f aca="false">G29-F29</f>
+        <v>-4.21135745711371</v>
+      </c>
+      <c r="I29" s="57" t="s">
+        <v>353</v>
+      </c>
+      <c r="J29" s="57" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="C30" s="22" t="n">
         <v>5.00003983050848</v>
       </c>
-      <c r="D29" s="54" t="n">
+      <c r="D30" s="55" t="n">
         <v>0.0987113654453513</v>
       </c>
-      <c r="E29" s="24" t="n">
+      <c r="E30" s="24" t="n">
         <v>5.42597861068479</v>
       </c>
-      <c r="F29" s="24" t="n">
+      <c r="F30" s="24" t="n">
         <v>18.1722</v>
       </c>
-      <c r="G29" s="24" t="n">
+      <c r="G30" s="24" t="n">
         <v>9.64994419208216</v>
       </c>
-      <c r="H29" s="55" t="n">
-        <f aca="false">G29-F29</f>
+      <c r="H30" s="56" t="n">
+        <f aca="false">G30-F30</f>
         <v>-8.52225580791784</v>
       </c>
-      <c r="I29" s="56" t="s">
-        <v>295</v>
-      </c>
-      <c r="J29" s="56" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="12" t="s">
-        <v>309</v>
-      </c>
-      <c r="I30" s="33" t="n">
-        <f aca="false">COUNTIFS(I18:I29,"Yes",J18:J29,"Yes")</f>
+      <c r="I30" s="57" t="s">
+        <v>353</v>
+      </c>
+      <c r="J30" s="57" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="12" t="s">
+        <v>367</v>
+      </c>
+      <c r="I31" s="33" t="n">
+        <f aca="false">COUNTIFS(I19:I30,"Yes",J19:J30,"Yes")</f>
         <v>0</v>
       </c>
-      <c r="J30" s="33" t="n">
-        <f aca="false">ROWS(I18:I29)</f>
+      <c r="J31" s="33" t="n">
+        <f aca="false">ROWS(I19:I30)</f>
         <v>12</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="13"/>
+    <row r="32" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="13" t="s">
+        <v>368</v>
+      </c>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C35" s="54" t="s">
+        <v>370</v>
+      </c>
+      <c r="D35" s="54"/>
+      <c r="E35" s="54"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="54" t="s">
+        <v>264</v>
+      </c>
+      <c r="H35" s="54"/>
+      <c r="I35" s="54"/>
+      <c r="J35" s="54"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="13"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="13"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="H39" s="13"/>
+      <c r="I39" s="13"/>
+      <c r="J39" s="13"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13"/>
+      <c r="J40" s="13"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>389</v>
+      </c>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="H41" s="13"/>
+      <c r="I41" s="13"/>
+      <c r="J41" s="13"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>392</v>
+      </c>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="H42" s="13"/>
+      <c r="I42" s="13"/>
+      <c r="J42" s="13"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="H43" s="13"/>
+      <c r="I43" s="13"/>
+      <c r="J43" s="13"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>398</v>
+      </c>
+      <c r="D44" s="13"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="H44" s="13"/>
+      <c r="I44" s="13"/>
+      <c r="J44" s="13"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="3" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="B48" s="22" t="n">
+        <v>33.6132097525627</v>
+      </c>
+      <c r="C48" s="22" t="n">
+        <v>34.3958205576648</v>
+      </c>
+      <c r="D48" s="22" t="n">
+        <v>15.9256485696014</v>
+      </c>
+      <c r="E48" s="22" t="n">
+        <v>17.191661719765</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="B49" s="22" t="n">
+        <v>26.8654951172848</v>
+      </c>
+      <c r="C49" s="22" t="n">
+        <v>26.0017289873665</v>
+      </c>
+      <c r="D49" s="22" t="n">
+        <v>21.5258540457023</v>
+      </c>
+      <c r="E49" s="22" t="n">
+        <v>24.5247149754872</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="B50" s="22" t="n">
+        <v>20.7690535911191</v>
+      </c>
+      <c r="C50" s="22" t="n">
+        <v>20.9223396076853</v>
+      </c>
+      <c r="D50" s="22" t="n">
+        <v>29.186022743742</v>
+      </c>
+      <c r="E50" s="22" t="n">
+        <v>28.6316636132406</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="B51" s="22" t="n">
+        <v>18.7522415390335</v>
+      </c>
+      <c r="C51" s="22" t="n">
+        <v>18.6801108472835</v>
+      </c>
+      <c r="D51" s="22" t="n">
+        <v>33.3624746409543</v>
+      </c>
+      <c r="E51" s="22" t="n">
+        <v>29.6519596915071</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="13" t="s">
+        <v>408</v>
+      </c>
+      <c r="B52" s="13"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="13"/>
+      <c r="F52" s="13"/>
+      <c r="G52" s="13"/>
+      <c r="H52" s="13"/>
+      <c r="I52" s="13"/>
+      <c r="J52" s="13"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="3" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="B56" s="24" t="n">
+        <v>2.64748981533051</v>
+      </c>
+      <c r="C56" s="24" t="n">
+        <v>6.38844530102795</v>
+      </c>
+      <c r="D56" s="24" t="n">
+        <f aca="false">B56/C56</f>
+        <v>0.41441848377484</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="B57" s="24" t="n">
+        <v>0.81419330650505</v>
+      </c>
+      <c r="C57" s="24" t="n">
+        <v>3.00995090658157</v>
+      </c>
+      <c r="D57" s="24" t="n">
+        <f aca="false">B57/C57</f>
+        <v>0.270500527010169</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="B58" s="24" t="n">
+        <v>1.2509</v>
+      </c>
+      <c r="C58" s="24" t="n">
+        <v>1.1029599243161</v>
+      </c>
+      <c r="D58" s="24" t="n">
+        <f aca="false">B58/C58</f>
+        <v>1.1341300553378</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="B59" s="24" t="n">
+        <v>5.5452</v>
+      </c>
+      <c r="C59" s="24" t="n">
+        <v>5.47839169073092</v>
+      </c>
+      <c r="D59" s="24" t="n">
+        <f aca="false">B59/C59</f>
+        <v>1.01219487635068</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="B60" s="24" t="n">
+        <v>1.1657</v>
+      </c>
+      <c r="C60" s="24" t="n">
+        <v>1.45781561498416</v>
+      </c>
+      <c r="D60" s="24" t="n">
+        <f aca="false">B60/C60</f>
+        <v>0.799621013808849</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="B61" s="24" t="n">
+        <v>5.1587</v>
+      </c>
+      <c r="C61" s="24" t="n">
+        <v>5.89509655474887</v>
+      </c>
+      <c r="D61" s="24" t="n">
+        <f aca="false">B61/C61</f>
+        <v>0.875083207219794</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="B62" s="24" t="n">
+        <v>1.3887</v>
+      </c>
+      <c r="C62" s="24" t="n">
+        <v>1.44111857101676</v>
+      </c>
+      <c r="D62" s="24" t="n">
+        <f aca="false">B62/C62</f>
+        <v>0.96362646900055</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="B63" s="24" t="n">
+        <v>6.0299</v>
+      </c>
+      <c r="C63" s="24" t="n">
+        <v>5.80100176684177</v>
+      </c>
+      <c r="D63" s="24" t="n">
+        <f aca="false">B63/C63</f>
+        <v>1.03945839742139</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="12" t="s">
+        <v>422</v>
+      </c>
+      <c r="D64" s="27" t="n">
+        <f aca="false">MAX(D56:D63)</f>
+        <v>1.1341300553378</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="13" t="s">
+        <v>423</v>
+      </c>
+      <c r="B65" s="13"/>
+      <c r="C65" s="13"/>
+      <c r="D65" s="13"/>
+      <c r="E65" s="13"/>
+      <c r="F65" s="13"/>
+      <c r="G65" s="13"/>
+      <c r="H65" s="13"/>
+      <c r="I65" s="13"/>
+      <c r="J65" s="13"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="13" t="s">
+        <v>424</v>
+      </c>
+      <c r="B67" s="13"/>
+      <c r="C67" s="13"/>
+      <c r="D67" s="13"/>
+      <c r="E67" s="13"/>
+      <c r="F67" s="13"/>
+      <c r="G67" s="13"/>
+      <c r="H67" s="13"/>
+      <c r="I67" s="13"/>
+      <c r="J67" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="35">
     <mergeCell ref="C5:J5"/>
     <mergeCell ref="C6:J6"/>
     <mergeCell ref="C7:J7"/>
@@ -5023,8 +6365,32 @@
     <mergeCell ref="C11:J11"/>
     <mergeCell ref="C12:J12"/>
     <mergeCell ref="C13:J13"/>
-    <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="C14:J14"/>
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="G35:J35"/>
+    <mergeCell ref="C36:F36"/>
+    <mergeCell ref="G36:J36"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="G37:J37"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="G38:J38"/>
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="G39:J39"/>
+    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="G40:J40"/>
+    <mergeCell ref="C41:F41"/>
+    <mergeCell ref="G41:J41"/>
+    <mergeCell ref="C42:F42"/>
+    <mergeCell ref="G42:J42"/>
+    <mergeCell ref="C43:F43"/>
+    <mergeCell ref="G43:J43"/>
+    <mergeCell ref="C44:F44"/>
+    <mergeCell ref="G44:J44"/>
+    <mergeCell ref="A52:J52"/>
+    <mergeCell ref="A65:J65"/>
+    <mergeCell ref="A67:J67"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -5041,7 +6407,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="38"/>
@@ -5051,294 +6417,472 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>311</v>
+        <v>425</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>312</v>
+        <v>426</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>313</v>
+        <v>427</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>314</v>
+        <v>428</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>315</v>
+        <v>429</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>316</v>
+        <v>430</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>317</v>
+        <v>431</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>318</v>
+        <v>432</v>
       </c>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>319</v>
+        <v>433</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="s">
+        <v>434</v>
+      </c>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="13" t="s">
+        <v>436</v>
+      </c>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="s">
+        <v>438</v>
+      </c>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="13" t="s">
+        <v>440</v>
+      </c>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="13" t="s">
+        <v>441</v>
+      </c>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="13" t="s">
+        <v>442</v>
+      </c>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="13" t="s">
+        <v>443</v>
+      </c>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="13" t="s">
+        <v>444</v>
+      </c>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="13" t="s">
+        <v>446</v>
+      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
+      <c r="B27" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C27" s="4" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>183</v>
+        <v>449</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>189</v>
+        <v>451</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>193</v>
+        <v>453</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
-        <v>346</v>
+        <v>455</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>348</v>
+        <v>457</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>349</v>
+        <v>458</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>488</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="18">
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A24:C24"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
